--- a/Projekty - bodovací tabulka.xlsx
+++ b/Projekty - bodovací tabulka.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
@@ -1045,6 +1045,9 @@
         <v>1</v>
       </c>
       <c r="H17" s="8"/>
+      <c r="I17" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="B18" s="6" t="s">
@@ -1057,6 +1060,10 @@
         <f t="shared" ref="F18:F19" si="4">if(n(D18),D18,sum(C18:D18))</f>
         <v>2</v>
       </c>
+      <c r="I18" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="B19" s="6" t="s">
@@ -1093,6 +1100,9 @@
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="I21" s="8">
         <v>2.0</v>
       </c>
     </row>
@@ -1124,9 +1134,7 @@
       <c r="C24" s="7">
         <v>0.0</v>
       </c>
-      <c r="I24" s="8">
-        <v>0.0</v>
-      </c>
+      <c r="I24" s="8"/>
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="B25" s="6" t="s">
@@ -1138,6 +1146,9 @@
       <c r="F25" s="6">
         <f>if(n(E25),E25,sum(C25:D25))</f>
         <v>3</v>
+      </c>
+      <c r="I25" s="8">
+        <v>3.0</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1"/>
@@ -1202,6 +1213,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="I30" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="B31" s="6" t="s">
@@ -1213,6 +1227,9 @@
       <c r="F31" s="6">
         <f t="shared" si="5"/>
         <v>1</v>
+      </c>
+      <c r="I31" s="8">
+        <v>1.0</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1"/>
@@ -1307,6 +1324,9 @@
         <f t="shared" ref="F39:F41" si="7">if(n(E39),E39,sum(C39:D39))</f>
         <v>1</v>
       </c>
+      <c r="I39" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="B40" s="6" t="s">
@@ -1319,6 +1339,9 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
+      <c r="I40" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="B41" s="6" t="s">
@@ -1330,6 +1353,9 @@
       <c r="F41" s="6">
         <f t="shared" si="7"/>
         <v>2</v>
+      </c>
+      <c r="I41" s="8">
+        <v>2.0</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1"/>
@@ -1550,6 +1576,10 @@
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
+      <c r="I59" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="J59" s="8"/>
     </row>
     <row r="60" ht="12.75" customHeight="1"/>
     <row r="61" ht="12.75" customHeight="1">
@@ -1656,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="I68" s="8">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
@@ -1669,6 +1699,9 @@
       <c r="F69" s="6">
         <f t="shared" si="13"/>
         <v>2</v>
+      </c>
+      <c r="I69" s="8">
+        <v>2.0</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
@@ -1815,6 +1848,9 @@
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
+      <c r="I81" s="8">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="82" ht="12.75" customHeight="1"/>
     <row r="83" ht="12.75" customHeight="1">
@@ -1860,6 +1896,9 @@
         <f>if(n(E85),E85,sum(C85:D85))</f>
         <v>1</v>
       </c>
+      <c r="I85" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="86" ht="12.75" customHeight="1"/>
     <row r="87" ht="12.75" customHeight="1">
@@ -1905,6 +1944,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
+      <c r="I89" s="8"/>
     </row>
     <row r="90" ht="12.75" customHeight="1">
       <c r="B90" s="6" t="s">
@@ -1917,6 +1957,9 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
+      <c r="I90" s="8">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="91" ht="12.75" customHeight="1">
       <c r="B91" s="11" t="s">
@@ -1929,6 +1972,10 @@
       <c r="F91" s="13">
         <v>2.0</v>
       </c>
+      <c r="I91" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="J91" s="8"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
       <c r="B92" s="11" t="s">
@@ -1986,9 +2033,7 @@
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="I96" s="8">
-        <v>1.0</v>
-      </c>
+      <c r="I96" s="8"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
       <c r="B97" s="6" t="s">
@@ -2012,6 +2057,9 @@
       <c r="F98" s="6">
         <f t="shared" si="17"/>
         <v>3</v>
+      </c>
+      <c r="I98" s="8">
+        <v>3.0</v>
       </c>
     </row>
     <row r="99" ht="12.75" customHeight="1"/>
@@ -2070,6 +2118,9 @@
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
+      <c r="I103" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="104" ht="12.75" customHeight="1">
       <c r="B104" s="6" t="s">
@@ -2115,6 +2166,9 @@
         <f t="shared" ref="F107:F108" si="19">if(n(E107),E107,sum(C107:D107))</f>
         <v>1</v>
       </c>
+      <c r="I107" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="108" ht="12.75" customHeight="1">
       <c r="B108" s="6" t="s">
@@ -2127,6 +2181,10 @@
         <f t="shared" si="19"/>
         <v>2</v>
       </c>
+      <c r="I108" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="J108" s="8"/>
     </row>
     <row r="109" ht="12.75" customHeight="1"/>
     <row r="110" ht="12.75" customHeight="1">
@@ -2234,6 +2292,9 @@
         <f t="shared" ref="F117:F118" si="21">if(n(E117),E117,sum(C117:E117))</f>
         <v>2</v>
       </c>
+      <c r="I117" s="8">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="118" ht="12.75" customHeight="1">
       <c r="B118" s="6" t="s">
@@ -2349,6 +2410,9 @@
         <v>1.0</v>
       </c>
       <c r="H128" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I128" s="8">
         <v>1.0</v>
       </c>
     </row>
